--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04741DD7-D42B-4F70-83E8-78C20B8CFD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC685C8-9417-4C25-88E8-92DB638A84A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -396,7 +396,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -607,7 +607,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
@@ -625,7 +625,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="21" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
@@ -687,7 +687,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="21" customFormat="1">
       <c r="A2" s="22"/>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -1066,9 +1066,7 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
+      <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
